--- a/data/trans_orig/P36B13-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36B13-Estudios-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>326291</t>
+          <t>326383</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>383595</t>
+          <t>381018</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>517704</t>
+          <t>519101</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>585446</t>
+          <t>585526</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>861306</t>
+          <t>863078</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>947492</t>
+          <t>944990</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>54,67%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>161515</t>
+          <t>161996</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>207092</t>
+          <t>207819</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>199256</t>
+          <t>199503</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>253578</t>
+          <t>256951</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>375172</t>
+          <t>376871</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>449953</t>
+          <t>449484</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,0%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>120346</t>
+          <t>117557</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>163195</t>
+          <t>163121</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136391</t>
+          <t>135105</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>182321</t>
+          <t>180919</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>264200</t>
+          <t>262122</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>326952</t>
+          <t>327819</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,97%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46234</t>
+          <t>48417</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>78103</t>
+          <t>79885</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33030</t>
+          <t>31535</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58289</t>
+          <t>59084</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>89662</t>
+          <t>87217</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>131780</t>
+          <t>127485</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>2835</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12356</t>
+          <t>12370</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4475</t>
+          <t>4140</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2910</t>
+          <t>2908</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13440</t>
+          <t>12749</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>424067</t>
+          <t>422586</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>503329</t>
+          <t>501453</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>481057</t>
+          <t>482534</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>560471</t>
+          <t>561793</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>929399</t>
+          <t>928625</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1046567</t>
+          <t>1040940</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,73%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>581055</t>
+          <t>586543</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>668137</t>
+          <t>669350</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>602446</t>
+          <t>603412</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>689900</t>
+          <t>685238</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1209502</t>
+          <t>1206083</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1329896</t>
+          <t>1332670</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,94%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>636454</t>
+          <t>640216</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>723859</t>
+          <t>727686</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>582816</t>
+          <t>581022</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>663624</t>
+          <t>665529</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1242228</t>
+          <t>1243789</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1362868</t>
+          <t>1363258</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,69%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>232610</t>
+          <t>235261</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>294868</t>
+          <t>292585</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>145098</t>
+          <t>147793</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>197185</t>
+          <t>195668</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>390778</t>
+          <t>392126</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>472937</t>
+          <t>471603</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,66%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25148</t>
+          <t>24059</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>48361</t>
+          <t>48127</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13109</t>
+          <t>13907</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>32398</t>
+          <t>32632</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>42654</t>
+          <t>41484</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>73225</t>
+          <t>72873</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>113093</t>
+          <t>111823</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>154937</t>
+          <t>152780</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>112559</t>
+          <t>110557</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>154483</t>
+          <t>153629</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>235214</t>
+          <t>233820</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>292272</t>
+          <t>294284</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,97%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>155986</t>
+          <t>156453</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>201549</t>
+          <t>202375</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>189856</t>
+          <t>187975</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>235628</t>
+          <t>233075</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>356671</t>
+          <t>353393</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>424257</t>
+          <t>419630</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>38,46%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>164858</t>
+          <t>166649</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>211479</t>
+          <t>212443</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>146698</t>
+          <t>145642</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>187924</t>
+          <t>189028</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>326730</t>
+          <t>324715</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>392020</t>
+          <t>385866</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>35,36%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29442</t>
+          <t>29609</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>54259</t>
+          <t>55775</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>25855</t>
+          <t>25841</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48251</t>
+          <t>47861</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>62023</t>
+          <t>61264</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>96127</t>
+          <t>93264</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11867</t>
+          <t>11506</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>980</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8845</t>
+          <t>9542</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16092</t>
+          <t>17256</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>895364</t>
+          <t>892037</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1000854</t>
+          <t>998419</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1148440</t>
+          <t>1142172</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1266863</t>
+          <t>1263957</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2075496</t>
+          <t>2076728</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2228370</t>
+          <t>2234266</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,54%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>933572</t>
+          <t>934869</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1041594</t>
+          <t>1039052</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1023590</t>
+          <t>1028647</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1134728</t>
+          <t>1140339</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1993072</t>
+          <t>1999725</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2142447</t>
+          <t>2152102</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,35%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>960787</t>
+          <t>961781</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1068455</t>
+          <t>1066326</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>892827</t>
+          <t>892623</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1002430</t>
+          <t>994049</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1886862</t>
+          <t>1882174</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2033612</t>
+          <t>2027000</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,52%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>336721</t>
+          <t>334205</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>405297</t>
+          <t>404334</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>218410</t>
+          <t>218653</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>281843</t>
+          <t>281787</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>572672</t>
+          <t>572526</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>664283</t>
+          <t>663725</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>33303</t>
+          <t>33683</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>60222</t>
+          <t>61087</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>17085</t>
+          <t>17247</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>37220</t>
+          <t>36913</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>54749</t>
+          <t>54735</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>91530</t>
+          <t>88902</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -3685,32 +3685,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>230813</t>
+          <t>255010</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>209216</t>
+          <t>232736</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>276607</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3720,32 +3720,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>434863</t>
+          <t>471272</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>413927</t>
+          <t>450223</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>455780</t>
+          <t>493883</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3755,32 +3755,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>665676</t>
+          <t>726282</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>635420</t>
+          <t>691068</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>694005</t>
+          <t>759022</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>54,25%</t>
         </is>
       </c>
     </row>
@@ -3798,32 +3798,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>160129</t>
+          <t>180974</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>139080</t>
+          <t>158515</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>179657</t>
+          <t>203408</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3833,32 +3833,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>182509</t>
+          <t>201503</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>165557</t>
+          <t>183745</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>201736</t>
+          <t>223822</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3868,32 +3868,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>342638</t>
+          <t>382477</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>315944</t>
+          <t>354674</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>369406</t>
+          <t>414685</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,64%</t>
         </is>
       </c>
     </row>
@@ -3911,32 +3911,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>86634</t>
+          <t>100364</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>70935</t>
+          <t>82717</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>105202</t>
+          <t>121056</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3946,32 +3946,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>118866</t>
+          <t>127767</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>101578</t>
+          <t>111379</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>138511</t>
+          <t>146206</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3981,32 +3981,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>205501</t>
+          <t>228131</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>185789</t>
+          <t>203903</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>235823</t>
+          <t>255171</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,24%</t>
         </is>
       </c>
     </row>
@@ -4024,32 +4024,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30147</t>
+          <t>34815</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20917</t>
+          <t>24066</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43713</t>
+          <t>48384</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4059,32 +4059,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19269</t>
+          <t>21496</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12769</t>
+          <t>14114</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28169</t>
+          <t>30953</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4094,32 +4094,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>49416</t>
+          <t>56312</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37373</t>
+          <t>43382</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64610</t>
+          <t>70696</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -4137,32 +4137,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5784</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2245</t>
+          <t>1739</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13824</t>
+          <t>13153</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4207,32 +4207,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>5784</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13347</t>
+          <t>13260</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -4250,17 +4250,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>513507</t>
+          <t>577112</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>513507</t>
+          <t>577112</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>513507</t>
+          <t>577112</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4285,17 +4285,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4320,17 +4320,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1269015</t>
+          <t>1399150</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1269015</t>
+          <t>1399150</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1269015</t>
+          <t>1399150</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4367,32 +4367,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>419356</t>
+          <t>459588</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>282392</t>
+          <t>420990</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>484662</t>
+          <t>502724</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4402,32 +4402,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>709396</t>
+          <t>578355</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>539969</t>
+          <t>543618</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1084634</t>
+          <t>611457</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4437,32 +4437,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1128752</t>
+          <t>1037942</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>916498</t>
+          <t>985579</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1638747</t>
+          <t>1090349</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>24,82%</t>
         </is>
       </c>
     </row>
@@ -4480,32 +4480,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>802226</t>
+          <t>867370</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>551290</t>
+          <t>817192</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>920598</t>
+          <t>919472</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4515,32 +4515,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>817497</t>
+          <t>904865</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>611058</t>
+          <t>858992</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>924125</t>
+          <t>947034</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4550,32 +4550,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1619723</t>
+          <t>1772235</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1322952</t>
+          <t>1707583</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1802353</t>
+          <t>1838894</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>41,87%</t>
         </is>
       </c>
     </row>
@@ -4593,32 +4593,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>653418</t>
+          <t>710898</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>420583</t>
+          <t>657635</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>752146</t>
+          <t>763505</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4628,32 +4628,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>621049</t>
+          <t>583019</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>464755</t>
+          <t>542961</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>779668</t>
+          <t>624326</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4663,32 +4663,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1274467</t>
+          <t>1293917</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1048341</t>
+          <t>1233269</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1462519</t>
+          <t>1360056</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>30,97%</t>
         </is>
       </c>
     </row>
@@ -4706,32 +4706,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>143338</t>
+          <t>163145</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>94699</t>
+          <t>134557</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>179351</t>
+          <t>198564</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4741,32 +4741,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>75201</t>
+          <t>86370</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53412</t>
+          <t>70209</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>96537</t>
+          <t>106949</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4776,32 +4776,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>218539</t>
+          <t>249515</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>172375</t>
+          <t>212037</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>261980</t>
+          <t>290635</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -4819,32 +4819,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>269274</t>
+          <t>26899</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>23460</t>
+          <t>16168</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>933650</t>
+          <t>42635</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4854,32 +4854,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>11663</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>5884</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15229</t>
+          <t>22167</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4889,32 +4889,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>276956</t>
+          <t>38563</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>29556</t>
+          <t>27424</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1026164</t>
+          <t>55488</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -4932,17 +4932,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2287612</t>
+          <t>2227901</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2287612</t>
+          <t>2227901</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2287612</t>
+          <t>2227901</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4967,17 +4967,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2230824</t>
+          <t>2164272</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2230824</t>
+          <t>2164272</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2230824</t>
+          <t>2164272</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5002,17 +5002,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>4518437</t>
+          <t>4392173</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4518437</t>
+          <t>4392173</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4518437</t>
+          <t>4392173</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5049,32 +5049,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>181431</t>
+          <t>200432</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>158860</t>
+          <t>176219</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>204428</t>
+          <t>225045</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5084,32 +5084,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>205717</t>
+          <t>229695</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>185768</t>
+          <t>208276</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>227300</t>
+          <t>252961</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5119,32 +5119,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>387149</t>
+          <t>430127</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>358308</t>
+          <t>399879</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>421748</t>
+          <t>465871</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,26%</t>
         </is>
       </c>
     </row>
@@ -5162,32 +5162,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>308331</t>
+          <t>326935</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>281739</t>
+          <t>297872</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>338483</t>
+          <t>354810</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5197,32 +5197,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>317151</t>
+          <t>352468</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>295033</t>
+          <t>326898</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>340558</t>
+          <t>376016</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5232,32 +5232,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>625483</t>
+          <t>679403</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>588288</t>
+          <t>644294</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>660258</t>
+          <t>715254</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>49,52%</t>
         </is>
       </c>
     </row>
@@ -5275,32 +5275,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>128846</t>
+          <t>152119</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>128201</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>151282</t>
+          <t>180402</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5310,32 +5310,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>111771</t>
+          <t>126355</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>95612</t>
+          <t>106034</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>131431</t>
+          <t>143906</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5345,32 +5345,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>240617</t>
+          <t>278474</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>214796</t>
+          <t>246224</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>269802</t>
+          <t>311485</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>21,57%</t>
         </is>
       </c>
     </row>
@@ -5388,27 +5388,27 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>25682</t>
+          <t>28554</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15845</t>
+          <t>17720</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39829</t>
+          <t>43858</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -5423,32 +5423,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>22188</t>
+          <t>22728</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13867</t>
+          <t>13570</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>33193</t>
+          <t>35689</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5458,32 +5458,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>47870</t>
+          <t>51282</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>33683</t>
+          <t>34835</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>66938</t>
+          <t>68906</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -5501,32 +5501,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2333</t>
+          <t>3548</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7621</t>
+          <t>9598</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -5546,12 +5546,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5096</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5571,32 +5571,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>3727</t>
+          <t>4999</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9634</t>
+          <t>11103</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -5614,17 +5614,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5649,17 +5649,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>658221</t>
+          <t>732697</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>658221</t>
+          <t>732697</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>658221</t>
+          <t>732697</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5684,17 +5684,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1304845</t>
+          <t>1444284</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1304845</t>
+          <t>1444284</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1304845</t>
+          <t>1444284</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5731,32 +5731,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>831600</t>
+          <t>915030</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>606226</t>
+          <t>863542</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>910418</t>
+          <t>967224</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5766,32 +5766,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1349977</t>
+          <t>1279322</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1191940</t>
+          <t>1225621</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1819826</t>
+          <t>1324441</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5801,32 +5801,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2181577</t>
+          <t>2194352</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1960103</t>
+          <t>2120003</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2605053</t>
+          <t>2269791</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>31,37%</t>
         </is>
       </c>
     </row>
@@ -5844,32 +5844,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1270686</t>
+          <t>1375280</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>986813</t>
+          <t>1312953</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1388425</t>
+          <t>1440073</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5879,32 +5879,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1317157</t>
+          <t>1458835</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1039355</t>
+          <t>1410651</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1425585</t>
+          <t>1512500</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5914,32 +5914,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2587843</t>
+          <t>2834115</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2234791</t>
+          <t>2751334</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2755885</t>
+          <t>2916725</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>40,31%</t>
         </is>
       </c>
     </row>
@@ -5957,32 +5957,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>868898</t>
+          <t>963381</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>654624</t>
+          <t>897399</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>960226</t>
+          <t>1025505</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5992,32 +5992,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>851686</t>
+          <t>837141</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>720195</t>
+          <t>789742</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1030126</t>
+          <t>888350</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6027,32 +6027,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1720584</t>
+          <t>1800523</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1506668</t>
+          <t>1721636</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1895380</t>
+          <t>1878273</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>25,96%</t>
         </is>
       </c>
     </row>
@@ -6070,32 +6070,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>199167</t>
+          <t>226514</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>152305</t>
+          <t>194388</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>233901</t>
+          <t>268953</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6105,32 +6105,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>116658</t>
+          <t>130595</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>92074</t>
+          <t>110103</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>142091</t>
+          <t>155157</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6140,32 +6140,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>315825</t>
+          <t>357109</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>263591</t>
+          <t>316962</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>360940</t>
+          <t>408047</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -6183,32 +6183,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>277391</t>
+          <t>36395</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>31572</t>
+          <t>24850</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1067640</t>
+          <t>54334</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6218,32 +6218,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>13114</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4795</t>
+          <t>7338</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16518</t>
+          <t>23228</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6253,32 +6253,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>286466</t>
+          <t>49509</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>39012</t>
+          <t>35430</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1143055</t>
+          <t>67290</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -6296,17 +6296,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3447743</t>
+          <t>3516601</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3447743</t>
+          <t>3516601</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3447743</t>
+          <t>3516601</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6331,17 +6331,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3644553</t>
+          <t>3719007</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3644553</t>
+          <t>3719007</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3644553</t>
+          <t>3719007</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6366,17 +6366,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7092296</t>
+          <t>7235608</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7092296</t>
+          <t>7235608</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7092296</t>
+          <t>7235608</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
